--- a/Team-Data/2008-09/1-16-2008-09.xlsx
+++ b/Team-Data/2008-09/1-16-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,25 +728,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" t="n">
         <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>0.59</v>
+        <v>0.605</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J2" t="n">
-        <v>78.8</v>
+        <v>78.5</v>
       </c>
       <c r="K2" t="n">
         <v>0.457</v>
@@ -688,16 +755,16 @@
         <v>8.1</v>
       </c>
       <c r="M2" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.377</v>
+        <v>0.38</v>
       </c>
       <c r="O2" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P2" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="Q2" t="n">
         <v>0.741</v>
@@ -706,7 +773,7 @@
         <v>10.7</v>
       </c>
       <c r="S2" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T2" t="n">
         <v>40.3</v>
@@ -715,7 +782,7 @@
         <v>21.6</v>
       </c>
       <c r="V2" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W2" t="n">
         <v>6.9</v>
@@ -724,31 +791,31 @@
         <v>4.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AA2" t="n">
         <v>20.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.40000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG2" t="n">
         <v>10</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>25</v>
@@ -757,7 +824,7 @@
         <v>22</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK2" t="n">
         <v>11</v>
@@ -769,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
         <v>23</v>
@@ -781,16 +848,16 @@
         <v>29</v>
       </c>
       <c r="AR2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
         <v>6</v>
@@ -805,7 +872,7 @@
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA2" t="n">
         <v>22</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -843,88 +910,88 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
         <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.775</v>
+        <v>0.78</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J3" t="n">
-        <v>76.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.48</v>
+        <v>0.479</v>
       </c>
       <c r="L3" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M3" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>0.376</v>
+        <v>0.373</v>
       </c>
       <c r="O3" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="P3" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.773</v>
+        <v>0.768</v>
       </c>
       <c r="R3" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="U3" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="V3" t="n">
         <v>16.1</v>
       </c>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
         <v>23.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>101</v>
+        <v>100.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>4</v>
@@ -933,25 +1000,25 @@
         <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ3" t="n">
         <v>29</v>
       </c>
       <c r="AK3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AM3" t="n">
         <v>18</v>
       </c>
       <c r="AN3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
         <v>5</v>
@@ -960,7 +1027,7 @@
         <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
@@ -981,7 +1048,7 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -990,7 +1057,7 @@
         <v>26</v>
       </c>
       <c r="BA3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
@@ -1115,7 +1182,7 @@
         <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1127,7 +1194,7 @@
         <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM4" t="n">
         <v>25</v>
@@ -1139,16 +1206,16 @@
         <v>20</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR4" t="n">
         <v>22</v>
       </c>
       <c r="AS4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
         <v>29</v>
@@ -1160,7 +1227,7 @@
         <v>26</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX4" t="n">
         <v>21</v>
@@ -1172,7 +1239,7 @@
         <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>0.436</v>
+        <v>0.45</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
@@ -1225,73 +1292,73 @@
         <v>37.1</v>
       </c>
       <c r="J5" t="n">
-        <v>84.2</v>
+        <v>83.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.441</v>
+        <v>0.443</v>
       </c>
       <c r="L5" t="n">
         <v>6.3</v>
       </c>
       <c r="M5" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N5" t="n">
         <v>0.381</v>
       </c>
       <c r="O5" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="R5" t="n">
         <v>11.6</v>
       </c>
       <c r="S5" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
         <v>41.7</v>
       </c>
       <c r="U5" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W5" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X5" t="n">
         <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>99.2</v>
+        <v>99.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.5</v>
+        <v>-3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
@@ -1300,13 +1367,13 @@
         <v>7</v>
       </c>
       <c r="AI5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ5" t="n">
         <v>4</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
         <v>19</v>
@@ -1315,16 +1382,16 @@
         <v>20</v>
       </c>
       <c r="AN5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AP5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR5" t="n">
         <v>12</v>
@@ -1333,34 +1400,34 @@
         <v>15</v>
       </c>
       <c r="AT5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV5" t="n">
         <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
         <v>22</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -1392,49 +1459,49 @@
         <v>37</v>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.838</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J6" t="n">
-        <v>78.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.479</v>
       </c>
       <c r="L6" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="M6" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.363</v>
+        <v>0.357</v>
       </c>
       <c r="O6" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="P6" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.759</v>
+        <v>0.757</v>
       </c>
       <c r="R6" t="n">
         <v>10.6</v>
       </c>
       <c r="S6" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
         <v>41.6</v>
@@ -1443,40 +1510,40 @@
         <v>20.3</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.4</v>
       </c>
       <c r="W6" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X6" t="n">
         <v>5.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.4</v>
+        <v>101.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.4</v>
+        <v>11.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>23</v>
@@ -1488,40 +1555,40 @@
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AM6" t="n">
         <v>7</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW6" t="n">
         <v>7</v>
@@ -1530,13 +1597,13 @@
         <v>3</v>
       </c>
       <c r="AY6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
         <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
@@ -1661,13 +1728,13 @@
         <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="n">
         <v>6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK7" t="n">
         <v>17</v>
@@ -1679,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
         <v>28</v>
@@ -1697,7 +1764,7 @@
         <v>3</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
@@ -1706,13 +1773,13 @@
         <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
         <v>8</v>
       </c>
       <c r="AY7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
         <v>2</v>
@@ -1721,7 +1788,7 @@
         <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>3.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
         <v>21</v>
@@ -1849,7 +1916,7 @@
         <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1861,7 +1928,7 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
         <v>24</v>
@@ -1879,13 +1946,13 @@
         <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1897,7 +1964,7 @@
         <v>28</v>
       </c>
       <c r="AZ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E9" t="n">
         <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.579</v>
+        <v>0.595</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1953,43 +2020,43 @@
         <v>35.8</v>
       </c>
       <c r="J9" t="n">
-        <v>79.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0.452</v>
       </c>
       <c r="L9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M9" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.345</v>
+        <v>0.347</v>
       </c>
       <c r="O9" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="P9" t="n">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.744</v>
+        <v>0.748</v>
       </c>
       <c r="R9" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S9" t="n">
         <v>30.3</v>
       </c>
       <c r="T9" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="U9" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V9" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="W9" t="n">
         <v>6.7</v>
@@ -2001,28 +2068,28 @@
         <v>3.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
       </c>
       <c r="AF9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
         <v>13</v>
@@ -2031,7 +2098,7 @@
         <v>24</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
         <v>15</v>
@@ -2043,40 +2110,40 @@
         <v>26</v>
       </c>
       <c r="AN9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AQ9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV9" t="n">
         <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
@@ -2088,7 +2155,7 @@
         <v>27</v>
       </c>
       <c r="BC9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -2117,67 +2184,67 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
         <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.293</v>
+        <v>0.275</v>
       </c>
       <c r="H10" t="n">
         <v>48.7</v>
       </c>
       <c r="I10" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="J10" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="L10" t="n">
         <v>6.4</v>
       </c>
       <c r="M10" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.35</v>
+        <v>0.346</v>
       </c>
       <c r="O10" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="P10" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.76</v>
+        <v>0.758</v>
       </c>
       <c r="R10" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S10" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="T10" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U10" t="n">
         <v>20.3</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Y10" t="n">
         <v>5.7</v>
@@ -2186,16 +2253,16 @@
         <v>21.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>106.8</v>
+        <v>106.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-5.6</v>
+        <v>-5.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2204,7 +2271,7 @@
         <v>26</v>
       </c>
       <c r="AG10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH10" t="n">
         <v>6</v>
@@ -2213,19 +2280,19 @@
         <v>3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="n">
         <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -2234,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR10" t="n">
         <v>3</v>
@@ -2243,13 +2310,13 @@
         <v>16</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
         <v>16</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
@@ -2270,7 +2337,7 @@
         <v>2</v>
       </c>
       <c r="BC10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2444,16 @@
         <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
@@ -2395,13 +2462,13 @@
         <v>29</v>
       </c>
       <c r="AJ11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK11" t="n">
         <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM11" t="n">
         <v>10</v>
@@ -2410,7 +2477,7 @@
         <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP11" t="n">
         <v>18</v>
@@ -2425,10 +2492,10 @@
         <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV11" t="n">
         <v>13</v>
@@ -2440,13 +2507,13 @@
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ11" t="n">
         <v>3</v>
       </c>
       <c r="BA11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
         <v>21</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
         <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>0.375</v>
+        <v>0.359</v>
       </c>
       <c r="H12" t="n">
         <v>48.8</v>
       </c>
       <c r="I12" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="J12" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.455</v>
@@ -2508,34 +2575,34 @@
         <v>7.4</v>
       </c>
       <c r="M12" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.365</v>
+        <v>0.366</v>
       </c>
       <c r="O12" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="P12" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0.804</v>
       </c>
       <c r="R12" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S12" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T12" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="U12" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V12" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="W12" t="n">
         <v>7.1</v>
@@ -2544,28 +2611,28 @@
         <v>5.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.9</v>
+        <v>104.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG12" t="n">
         <v>23</v>
@@ -2577,13 +2644,13 @@
         <v>2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK12" t="n">
         <v>14</v>
       </c>
       <c r="AL12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM12" t="n">
         <v>8</v>
@@ -2592,28 +2659,28 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AQ12" t="n">
         <v>5</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AS12" t="n">
         <v>2</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="n">
         <v>3</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW12" t="n">
         <v>16</v>
@@ -2622,19 +2689,19 @@
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-7.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,10 +2820,10 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2774,7 +2841,7 @@
         <v>30</v>
       </c>
       <c r="AO13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP13" t="n">
         <v>23</v>
@@ -2786,10 +2853,10 @@
         <v>6</v>
       </c>
       <c r="AS13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -2848,13 +2915,13 @@
         <v>38</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>0.789</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
@@ -2863,76 +2930,76 @@
         <v>39.7</v>
       </c>
       <c r="J14" t="n">
-        <v>83.8</v>
+        <v>83.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474</v>
+        <v>0.476</v>
       </c>
       <c r="L14" t="n">
         <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.378</v>
+        <v>0.384</v>
       </c>
       <c r="O14" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="P14" t="n">
-        <v>27.9</v>
+        <v>27.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R14" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>32</v>
       </c>
       <c r="T14" t="n">
-        <v>43.8</v>
+        <v>44.1</v>
       </c>
       <c r="U14" t="n">
         <v>23.2</v>
       </c>
       <c r="V14" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W14" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.9</v>
+        <v>107.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>29</v>
@@ -2944,25 +3011,25 @@
         <v>5</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AM14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
         <v>7</v>
@@ -2977,16 +3044,16 @@
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
         <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
         <v>8</v>
@@ -2998,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E15" t="n">
         <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G15" t="n">
-        <v>0.282</v>
+        <v>0.289</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="J15" t="n">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L15" t="n">
         <v>4.4</v>
@@ -3057,31 +3124,31 @@
         <v>13.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.32</v>
+        <v>0.322</v>
       </c>
       <c r="O15" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="P15" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.756</v>
+        <v>0.754</v>
       </c>
       <c r="R15" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="T15" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="U15" t="n">
         <v>16.7</v>
       </c>
       <c r="V15" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W15" t="n">
         <v>7.5</v>
@@ -3093,55 +3160,55 @@
         <v>5.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA15" t="n">
         <v>21.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.9</v>
+        <v>-5.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF15" t="n">
         <v>25</v>
       </c>
       <c r="AG15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH15" t="n">
         <v>9</v>
       </c>
       <c r="AI15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK15" t="n">
         <v>16</v>
       </c>
       <c r="AL15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM15" t="n">
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
@@ -3150,7 +3217,7 @@
         <v>26</v>
       </c>
       <c r="AS15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT15" t="n">
         <v>30</v>
@@ -3162,25 +3229,25 @@
         <v>16</v>
       </c>
       <c r="AW15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX15" t="n">
         <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ15" t="n">
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB15" t="n">
         <v>28</v>
       </c>
       <c r="BC15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
@@ -3299,7 +3366,7 @@
         <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI16" t="n">
         <v>19</v>
@@ -3320,10 +3387,10 @@
         <v>18</v>
       </c>
       <c r="AO16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
         <v>28</v>
@@ -3362,7 +3429,7 @@
         <v>22</v>
       </c>
       <c r="BC16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -3394,61 +3461,61 @@
         <v>41</v>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>0.488</v>
+        <v>0.463</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="J17" t="n">
-        <v>81.8</v>
+        <v>81.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M17" t="n">
         <v>15.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.345</v>
+        <v>0.341</v>
       </c>
       <c r="O17" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="P17" t="n">
-        <v>25</v>
+        <v>24.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.783</v>
+        <v>0.779</v>
       </c>
       <c r="R17" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S17" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T17" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U17" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="V17" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="W17" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X17" t="n">
         <v>3.5</v>
@@ -3457,16 +3524,16 @@
         <v>4.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,37 +3542,37 @@
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
         <v>14</v>
       </c>
       <c r="AJ17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AK17" t="n">
         <v>20</v>
       </c>
       <c r="AL17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM17" t="n">
         <v>24</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>10</v>
@@ -3514,7 +3581,7 @@
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT17" t="n">
         <v>11</v>
@@ -3526,7 +3593,7 @@
         <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3541,7 +3608,7 @@
         <v>6</v>
       </c>
       <c r="BB17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC17" t="n">
         <v>14</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -3573,85 +3640,85 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
         <v>26</v>
       </c>
       <c r="G18" t="n">
-        <v>0.316</v>
+        <v>0.297</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="J18" t="n">
-        <v>83.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K18" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M18" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O18" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P18" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="Q18" t="n">
         <v>0.759</v>
       </c>
       <c r="R18" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="S18" t="n">
         <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="U18" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V18" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W18" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y18" t="n">
         <v>6.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="AA18" t="n">
         <v>20.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.9</v>
+        <v>-4.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>24</v>
@@ -3666,10 +3733,10 @@
         <v>8</v>
       </c>
       <c r="AI18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK18" t="n">
         <v>28</v>
@@ -3681,34 +3748,34 @@
         <v>22</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AR18" t="n">
         <v>5</v>
       </c>
       <c r="AS18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV18" t="n">
         <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AX18" t="n">
         <v>23</v>
@@ -3717,13 +3784,13 @@
         <v>30</v>
       </c>
       <c r="AZ18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC18" t="n">
         <v>24</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3900,19 @@
         <v>-2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI19" t="n">
         <v>25</v>
@@ -3854,7 +3921,7 @@
         <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
         <v>5</v>
@@ -3863,7 +3930,7 @@
         <v>6</v>
       </c>
       <c r="AN19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
         <v>7</v>
@@ -3887,7 +3954,7 @@
         <v>29</v>
       </c>
       <c r="AV19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW19" t="n">
         <v>24</v>
@@ -3896,13 +3963,13 @@
         <v>19</v>
       </c>
       <c r="AY19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ19" t="n">
         <v>27</v>
       </c>
       <c r="BA19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB19" t="n">
         <v>13</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" t="n">
         <v>23</v>
       </c>
       <c r="F20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>0.639</v>
+        <v>0.657</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>34.9</v>
+        <v>35.2</v>
       </c>
       <c r="J20" t="n">
-        <v>76.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.456</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>7.5</v>
@@ -3967,16 +4034,16 @@
         <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.388</v>
+        <v>0.391</v>
       </c>
       <c r="O20" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P20" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R20" t="n">
         <v>9.699999999999999</v>
@@ -3988,13 +4055,13 @@
         <v>39</v>
       </c>
       <c r="U20" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="V20" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W20" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X20" t="n">
         <v>4.1</v>
@@ -4006,19 +4073,19 @@
         <v>21</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>95.7</v>
+        <v>96.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AD20" t="n">
         <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
@@ -4030,22 +4097,22 @@
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AJ20" t="n">
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM20" t="n">
         <v>11</v>
       </c>
       <c r="AN20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO20" t="n">
         <v>22</v>
@@ -4063,7 +4130,7 @@
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU20" t="n">
         <v>26</v>
@@ -4072,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
         <v>26</v>
@@ -4081,16 +4148,16 @@
         <v>2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BB20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -4119,67 +4186,67 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E21" t="n">
         <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>0.395</v>
+        <v>0.405</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J21" t="n">
         <v>86.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.433</v>
+        <v>0.435</v>
       </c>
       <c r="L21" t="n">
         <v>10.4</v>
       </c>
       <c r="M21" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O21" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P21" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.799</v>
+        <v>0.8</v>
       </c>
       <c r="R21" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S21" t="n">
         <v>31.2</v>
       </c>
       <c r="T21" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U21" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V21" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W21" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X21" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
         <v>5.4</v>
@@ -4191,25 +4258,25 @@
         <v>18.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>103.1</v>
+        <v>103.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
         <v>21</v>
       </c>
       <c r="AF21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
         <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
@@ -4236,7 +4303,7 @@
         <v>27</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AR21" t="n">
         <v>15</v>
@@ -4251,7 +4318,7 @@
         <v>8</v>
       </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW21" t="n">
         <v>14</v>
@@ -4263,7 +4330,7 @@
         <v>22</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4272,7 +4339,7 @@
         <v>6</v>
       </c>
       <c r="BC21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -4301,19 +4368,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
         <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>0.195</v>
+        <v>0.175</v>
       </c>
       <c r="H22" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I22" t="n">
         <v>36.4</v>
@@ -4322,7 +4389,7 @@
         <v>81.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L22" t="n">
         <v>3.9</v>
@@ -4331,34 +4398,34 @@
         <v>10.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O22" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P22" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q22" t="n">
         <v>0.763</v>
       </c>
       <c r="R22" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S22" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="T22" t="n">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="U22" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V22" t="n">
         <v>16.5</v>
       </c>
       <c r="W22" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X22" t="n">
         <v>4.6</v>
@@ -4367,22 +4434,22 @@
         <v>5.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA22" t="n">
         <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>95.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.9</v>
+        <v>-7.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF22" t="n">
         <v>30</v>
@@ -4391,16 +4458,16 @@
         <v>30</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ22" t="n">
         <v>10</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4412,16 +4479,16 @@
         <v>14</v>
       </c>
       <c r="AO22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ22" t="n">
         <v>15</v>
       </c>
       <c r="AR22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS22" t="n">
         <v>11</v>
@@ -4430,13 +4497,13 @@
         <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX22" t="n">
         <v>20</v>
@@ -4445,10 +4512,10 @@
         <v>21</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB22" t="n">
         <v>25</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F23" t="n">
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8</v>
+        <v>0.795</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
@@ -4501,37 +4568,37 @@
         <v>36.3</v>
       </c>
       <c r="J23" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L23" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="M23" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="N23" t="n">
-        <v>0.402</v>
+        <v>0.401</v>
       </c>
       <c r="O23" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P23" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.719</v>
+        <v>0.721</v>
       </c>
       <c r="R23" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T23" t="n">
-        <v>42.9</v>
+        <v>42.6</v>
       </c>
       <c r="U23" t="n">
         <v>19.6</v>
@@ -4549,37 +4616,37 @@
         <v>3.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.2</v>
+        <v>102</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH23" t="n">
         <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
         <v>8</v>
@@ -4594,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="AO23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP23" t="n">
         <v>7</v>
@@ -4609,7 +4676,7 @@
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU23" t="n">
         <v>27</v>
@@ -4624,7 +4691,7 @@
         <v>4</v>
       </c>
       <c r="AY23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ23" t="n">
         <v>7</v>
@@ -4636,7 +4703,7 @@
         <v>7</v>
       </c>
       <c r="BC23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -4665,58 +4732,58 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
         <v>20</v>
       </c>
       <c r="G24" t="n">
-        <v>0.487</v>
+        <v>0.474</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J24" t="n">
-        <v>80.5</v>
+        <v>80.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M24" t="n">
         <v>12.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0.329</v>
+        <v>0.322</v>
       </c>
       <c r="O24" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P24" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.747</v>
+        <v>0.746</v>
       </c>
       <c r="R24" t="n">
         <v>12.7</v>
       </c>
       <c r="S24" t="n">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="T24" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U24" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V24" t="n">
         <v>15.5</v>
@@ -4731,22 +4798,22 @@
         <v>5.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA24" t="n">
         <v>20.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>96.2</v>
+        <v>95.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF24" t="n">
         <v>16</v>
@@ -4758,13 +4825,13 @@
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ24" t="n">
         <v>15</v>
       </c>
       <c r="AK24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4779,34 +4846,34 @@
         <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AQ24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR24" t="n">
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV24" t="n">
         <v>25</v>
       </c>
       <c r="AW24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX24" t="n">
         <v>9</v>
       </c>
       <c r="AY24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ24" t="n">
         <v>9</v>
@@ -4815,10 +4882,10 @@
         <v>21</v>
       </c>
       <c r="BB24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -4847,58 +4914,58 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25" t="n">
         <v>22</v>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G25" t="n">
-        <v>0.595</v>
+        <v>0.611</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J25" t="n">
-        <v>77.5</v>
+        <v>77.3</v>
       </c>
       <c r="K25" t="n">
         <v>0.498</v>
       </c>
       <c r="L25" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M25" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0.388</v>
+        <v>0.393</v>
       </c>
       <c r="O25" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="P25" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R25" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T25" t="n">
         <v>41.1</v>
       </c>
       <c r="U25" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V25" t="n">
         <v>16.2</v>
@@ -4910,31 +4977,31 @@
         <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z25" t="n">
         <v>20.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.5</v>
+        <v>104.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
       </c>
       <c r="AF25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG25" t="n">
         <v>9</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>11</v>
       </c>
       <c r="AH25" t="n">
         <v>20</v>
@@ -4943,19 +5010,19 @@
         <v>4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AM25" t="n">
         <v>16</v>
       </c>
       <c r="AN25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO25" t="n">
         <v>6</v>
@@ -4964,31 +5031,31 @@
         <v>6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
         <v>28</v>
       </c>
       <c r="AS25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -5029,55 +5096,55 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E26" t="n">
         <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26" t="n">
-        <v>0.632</v>
+        <v>0.615</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="J26" t="n">
-        <v>78.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.456</v>
       </c>
       <c r="L26" t="n">
         <v>7.6</v>
       </c>
       <c r="M26" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="O26" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="P26" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.778</v>
+        <v>0.775</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="T26" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U26" t="n">
         <v>20.5</v>
@@ -5089,46 +5156,46 @@
         <v>6.8</v>
       </c>
       <c r="X26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG26" t="n">
         <v>8</v>
       </c>
       <c r="AH26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>21</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>23</v>
-      </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
         <v>6</v>
@@ -5140,7 +5207,7 @@
         <v>5</v>
       </c>
       <c r="AO26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP26" t="n">
         <v>19</v>
@@ -5158,7 +5225,7 @@
         <v>21</v>
       </c>
       <c r="AU26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV26" t="n">
         <v>4</v>
@@ -5167,10 +5234,10 @@
         <v>22</v>
       </c>
       <c r="AX26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
         <v>13</v>
@@ -5182,7 +5249,7 @@
         <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -5211,106 +5278,106 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" t="n">
-        <v>0.244</v>
+        <v>0.25</v>
       </c>
       <c r="H27" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I27" t="n">
         <v>36.3</v>
       </c>
       <c r="J27" t="n">
-        <v>81.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K27" t="n">
-        <v>0.446</v>
+        <v>0.444</v>
       </c>
       <c r="L27" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M27" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.334</v>
+        <v>0.333</v>
       </c>
       <c r="O27" t="n">
-        <v>20.1</v>
+        <v>19.6</v>
       </c>
       <c r="P27" t="n">
-        <v>25.1</v>
+        <v>24.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.8</v>
+        <v>0.798</v>
       </c>
       <c r="R27" t="n">
         <v>10.5</v>
       </c>
       <c r="S27" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T27" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="U27" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="V27" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W27" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z27" t="n">
         <v>23.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG27" t="n">
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AK27" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
         <v>20</v>
@@ -5319,16 +5386,16 @@
         <v>17</v>
       </c>
       <c r="AN27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
         <v>23</v>
@@ -5340,25 +5407,25 @@
         <v>24</v>
       </c>
       <c r="AU27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX27" t="n">
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
       </c>
       <c r="BA27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB27" t="n">
         <v>14</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E28" t="n">
         <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
-        <v>0.658</v>
+        <v>0.676</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
       </c>
       <c r="I28" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J28" t="n">
-        <v>79.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.468</v>
+        <v>0.471</v>
       </c>
       <c r="L28" t="n">
         <v>8.4</v>
@@ -5423,31 +5490,31 @@
         <v>20.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.404</v>
+        <v>0.405</v>
       </c>
       <c r="O28" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="P28" t="n">
         <v>19.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.759</v>
+        <v>0.755</v>
       </c>
       <c r="R28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="T28" t="n">
         <v>39.7</v>
       </c>
       <c r="U28" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V28" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="W28" t="n">
         <v>5.6</v>
@@ -5456,22 +5523,22 @@
         <v>4.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z28" t="n">
         <v>18.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5480,16 +5547,16 @@
         <v>5</v>
       </c>
       <c r="AG28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
@@ -5510,13 +5577,13 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
         <v>25</v>
@@ -5531,10 +5598,10 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5543,10 +5610,10 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -5575,109 +5642,109 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29" t="n">
         <v>16</v>
       </c>
       <c r="F29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G29" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J29" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L29" t="n">
         <v>6.4</v>
       </c>
       <c r="M29" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N29" t="n">
-        <v>0.38</v>
+        <v>0.383</v>
       </c>
       <c r="O29" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="P29" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.826</v>
+        <v>0.828</v>
       </c>
       <c r="R29" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S29" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T29" t="n">
-        <v>39.2</v>
+        <v>38.9</v>
       </c>
       <c r="U29" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="V29" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W29" t="n">
         <v>6.5</v>
       </c>
       <c r="X29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y29" t="n">
         <v>4.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.4</v>
+        <v>-2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
       </c>
       <c r="AF29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
         <v>21</v>
       </c>
       <c r="AH29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>23</v>
       </c>
-      <c r="AJ29" t="n">
-        <v>22</v>
-      </c>
       <c r="AK29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AL29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AM29" t="n">
         <v>19</v>
@@ -5686,10 +5753,10 @@
         <v>7</v>
       </c>
       <c r="AO29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP29" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,22 +5765,22 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
         <v>7</v>
       </c>
       <c r="AV29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY29" t="n">
         <v>12</v>
@@ -5722,13 +5789,13 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F30" t="n">
         <v>16</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5775,19 +5842,19 @@
         <v>37.9</v>
       </c>
       <c r="J30" t="n">
-        <v>79.8</v>
+        <v>80</v>
       </c>
       <c r="K30" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="M30" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="N30" t="n">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="O30" t="n">
         <v>21.3</v>
@@ -5799,16 +5866,16 @@
         <v>0.77</v>
       </c>
       <c r="R30" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S30" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T30" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="U30" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="V30" t="n">
         <v>15.3</v>
@@ -5817,10 +5884,10 @@
         <v>8.9</v>
       </c>
       <c r="X30" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y30" t="n">
         <v>4.9</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>5</v>
       </c>
       <c r="Z30" t="n">
         <v>22.7</v>
@@ -5832,22 +5899,22 @@
         <v>101.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH30" t="n">
         <v>10</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>11</v>
       </c>
       <c r="AI30" t="n">
         <v>5</v>
@@ -5856,10 +5923,10 @@
         <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM30" t="n">
         <v>28</v>
@@ -5868,10 +5935,10 @@
         <v>24</v>
       </c>
       <c r="AO30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ30" t="n">
         <v>13</v>
@@ -5880,10 +5947,10 @@
         <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AT30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5895,7 +5962,7 @@
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY30" t="n">
         <v>15</v>
@@ -5904,13 +5971,13 @@
         <v>25</v>
       </c>
       <c r="BA30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB30" t="n">
         <v>8</v>
       </c>
       <c r="BC30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
         <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>0.205</v>
+        <v>0.184</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5966,31 +6033,31 @@
         <v>5.1</v>
       </c>
       <c r="M31" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.322</v>
+        <v>0.316</v>
       </c>
       <c r="O31" t="n">
         <v>16.6</v>
       </c>
       <c r="P31" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R31" t="n">
         <v>11.7</v>
       </c>
       <c r="S31" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="T31" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="U31" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V31" t="n">
         <v>13.5</v>
@@ -6014,16 +6081,16 @@
         <v>94.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.3</v>
+        <v>-6.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
@@ -6038,7 +6105,7 @@
         <v>12</v>
       </c>
       <c r="AK31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6047,7 +6114,7 @@
         <v>23</v>
       </c>
       <c r="AN31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO31" t="n">
         <v>29</v>
@@ -6056,7 +6123,7 @@
         <v>28</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR31" t="n">
         <v>10</v>
@@ -6068,16 +6135,16 @@
         <v>26</v>
       </c>
       <c r="AU31" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AV31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW31" t="n">
         <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY31" t="n">
         <v>16</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-16-2008-09</t>
+          <t>2009-01-16</t>
         </is>
       </c>
     </row>
